--- a/output/roomself_excel/11130.xlsx
+++ b/output/roomself_excel/11130.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>748893</v>
+        <v>101724</v>
       </c>
       <c r="D2" t="n">
-        <v>12164</v>
+        <v>2560</v>
       </c>
       <c r="E2" t="n">
-        <v>1117</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>242885</v>
+        <v>40410</v>
       </c>
       <c r="D3" t="n">
-        <v>4696</v>
+        <v>1628</v>
       </c>
       <c r="E3" t="n">
-        <v>669</v>
+        <v>194</v>
       </c>
       <c r="F3" t="n">
-        <v>294</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5980</v>
+        <v>38857</v>
       </c>
       <c r="D4" t="n">
-        <v>668</v>
+        <v>1632</v>
       </c>
       <c r="E4" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>33800</v>
+        <v>80040</v>
       </c>
       <c r="D5" t="n">
-        <v>1476</v>
+        <v>2312</v>
       </c>
       <c r="E5" t="n">
-        <v>191</v>
+        <v>230</v>
       </c>
       <c r="F5" t="n">
-        <v>95</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33240</v>
+        <v>421962</v>
       </c>
       <c r="D6" t="n">
-        <v>1572</v>
+        <v>6460</v>
       </c>
       <c r="E6" t="n">
-        <v>138</v>
+        <v>1117</v>
       </c>
       <c r="F6" t="n">
-        <v>98</v>
+        <v>483</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6480</v>
+        <v>117986</v>
       </c>
       <c r="D7" t="n">
-        <v>672</v>
+        <v>2748</v>
       </c>
       <c r="E7" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>282248</v>
+        <v>85808</v>
       </c>
       <c r="D8" t="n">
-        <v>5668</v>
+        <v>2376</v>
       </c>
       <c r="E8" t="n">
-        <v>1024</v>
+        <v>346</v>
       </c>
       <c r="F8" t="n">
-        <v>260</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>35411</v>
+        <v>33240</v>
       </c>
       <c r="D9" t="n">
-        <v>1756</v>
+        <v>1572</v>
       </c>
       <c r="E9" t="n">
-        <v>250</v>
+        <v>138</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30324</v>
+        <v>35411</v>
       </c>
       <c r="D10" t="n">
-        <v>1428</v>
+        <v>1756</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38857</v>
+        <v>70600</v>
       </c>
       <c r="D11" t="n">
-        <v>1632</v>
+        <v>2916</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12">
@@ -686,14 +686,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>59388</v>
+        <v>154725</v>
       </c>
       <c r="D12" t="n">
-        <v>1996</v>
+        <v>3960</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -708,14 +708,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>117986</v>
+        <v>34436</v>
       </c>
       <c r="D13" t="n">
-        <v>2748</v>
+        <v>1508</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>104690</v>
+        <v>19402</v>
       </c>
       <c r="D14" t="n">
-        <v>3588</v>
+        <v>1148</v>
       </c>
       <c r="E14" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>43183</v>
+        <v>59332</v>
       </c>
       <c r="D15" t="n">
-        <v>1664</v>
+        <v>2032</v>
       </c>
       <c r="E15" t="n">
-        <v>286</v>
+        <v>182</v>
       </c>
       <c r="F15" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>105408</v>
+        <v>112470</v>
       </c>
       <c r="D16" t="n">
-        <v>2704</v>
+        <v>2684</v>
       </c>
       <c r="E16" t="n">
-        <v>460</v>
+        <v>373</v>
       </c>
       <c r="F16" t="n">
-        <v>271</v>
+        <v>354</v>
       </c>
     </row>
     <row r="17">
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>59332</v>
+        <v>168039</v>
       </c>
       <c r="D18" t="n">
-        <v>2032</v>
+        <v>3376</v>
       </c>
       <c r="E18" t="n">
-        <v>182</v>
+        <v>475</v>
       </c>
       <c r="F18" t="n">
-        <v>28</v>
+        <v>294</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>112470</v>
+        <v>5980</v>
       </c>
       <c r="D19" t="n">
-        <v>2684</v>
+        <v>668</v>
       </c>
       <c r="E19" t="n">
-        <v>373</v>
+        <v>115</v>
       </c>
       <c r="F19" t="n">
-        <v>354</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>70600</v>
+        <v>33800</v>
       </c>
       <c r="D20" t="n">
-        <v>2916</v>
+        <v>1476</v>
       </c>
       <c r="E20" t="n">
-        <v>277</v>
+        <v>191</v>
       </c>
       <c r="F20" t="n">
-        <v>142</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21">
@@ -884,17 +884,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>85808</v>
+        <v>6480</v>
       </c>
       <c r="D21" t="n">
-        <v>2376</v>
+        <v>672</v>
       </c>
       <c r="E21" t="n">
-        <v>346</v>
+        <v>108</v>
       </c>
       <c r="F21" t="n">
         <v>28</v>
@@ -906,20 +906,152 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>19402</v>
+        <v>202208</v>
       </c>
       <c r="D22" t="n">
-        <v>1148</v>
+        <v>4748</v>
       </c>
       <c r="E22" t="n">
-        <v>178</v>
+        <v>794</v>
       </c>
       <c r="F22" t="n">
-        <v>28</v>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>30324</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1428</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>70482</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2156</v>
+      </c>
+      <c r="E24" t="n">
+        <v>295</v>
+      </c>
+      <c r="F24" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>59388</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1996</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>104690</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3588</v>
+      </c>
+      <c r="E26" t="n">
+        <v>177</v>
+      </c>
+      <c r="F26" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>43183</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1664</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>105408</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2704</v>
+      </c>
+      <c r="E28" t="n">
+        <v>460</v>
+      </c>
+      <c r="F28" t="n">
+        <v>271</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/11130.xlsx
+++ b/output/roomself_excel/11130.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>2560</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +525,20 @@
       <c r="D3" t="n">
         <v>1628</v>
       </c>
-      <c r="E3" t="n">
-        <v>194</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>83</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="G3" t="n">
+        <v>27</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +555,12 @@
       <c r="D4" t="n">
         <v>1632</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +577,20 @@
       <c r="D5" t="n">
         <v>2312</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>230</v>
       </c>
-      <c r="F5" t="n">
-        <v>28</v>
-      </c>
+      <c r="G5" t="n">
+        <v>28</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,11 +607,27 @@
       <c r="D6" t="n">
         <v>6460</v>
       </c>
-      <c r="E6" t="n">
-        <v>1117</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>483</v>
+        <v>1090</v>
+      </c>
+      <c r="G6" t="n">
+        <v>28</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>739</v>
+      </c>
+      <c r="J6" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -585,12 +645,20 @@
       <c r="D7" t="n">
         <v>2748</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="G7" t="n">
+        <v>27</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,10 +675,26 @@
       <c r="D8" t="n">
         <v>2376</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>248</v>
+      </c>
+      <c r="G8" t="n">
+        <v>27</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>346</v>
       </c>
-      <c r="F8" t="n">
+      <c r="J8" t="n">
         <v>28</v>
       </c>
     </row>
@@ -629,12 +713,20 @@
       <c r="D9" t="n">
         <v>1572</v>
       </c>
-      <c r="E9" t="n">
-        <v>138</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>98</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="G9" t="n">
+        <v>28</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +743,12 @@
       <c r="D10" t="n">
         <v>1756</v>
       </c>
-      <c r="E10" t="n">
-        <v>250</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +765,20 @@
       <c r="D11" t="n">
         <v>2916</v>
       </c>
-      <c r="E11" t="n">
-        <v>277</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>142</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="G11" t="n">
+        <v>28</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +795,12 @@
       <c r="D12" t="n">
         <v>3960</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +817,12 @@
       <c r="D13" t="n">
         <v>1508</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +839,20 @@
       <c r="D14" t="n">
         <v>1148</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>178</v>
       </c>
-      <c r="F14" t="n">
-        <v>28</v>
-      </c>
+      <c r="G14" t="n">
+        <v>28</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +869,20 @@
       <c r="D15" t="n">
         <v>2032</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>182</v>
       </c>
-      <c r="F15" t="n">
-        <v>28</v>
-      </c>
+      <c r="G15" t="n">
+        <v>28</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,11 +899,27 @@
       <c r="D16" t="n">
         <v>2684</v>
       </c>
-      <c r="E16" t="n">
-        <v>373</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>354</v>
+        <v>326</v>
+      </c>
+      <c r="G16" t="n">
+        <v>28</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>345</v>
+      </c>
+      <c r="J16" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="17">
@@ -805,11 +937,27 @@
       <c r="D17" t="n">
         <v>3424</v>
       </c>
-      <c r="E17" t="n">
-        <v>564</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>354</v>
+        <v>325</v>
+      </c>
+      <c r="G17" t="n">
+        <v>22</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>530</v>
+      </c>
+      <c r="J17" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="18">
@@ -827,11 +975,27 @@
       <c r="D18" t="n">
         <v>3376</v>
       </c>
-      <c r="E18" t="n">
-        <v>475</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>294</v>
+        <v>267</v>
+      </c>
+      <c r="G18" t="n">
+        <v>28</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>249</v>
+      </c>
+      <c r="J18" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -849,12 +1013,20 @@
       <c r="D19" t="n">
         <v>668</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>115</v>
       </c>
-      <c r="F19" t="n">
-        <v>28</v>
-      </c>
+      <c r="G19" t="n">
+        <v>28</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1043,20 @@
       <c r="D20" t="n">
         <v>1476</v>
       </c>
-      <c r="E20" t="n">
-        <v>191</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>95</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="G20" t="n">
+        <v>28</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1073,20 @@
       <c r="D21" t="n">
         <v>672</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>108</v>
       </c>
-      <c r="F21" t="n">
-        <v>28</v>
-      </c>
+      <c r="G21" t="n">
+        <v>28</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,11 +1103,27 @@
       <c r="D22" t="n">
         <v>4748</v>
       </c>
-      <c r="E22" t="n">
-        <v>794</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>260</v>
+        <v>231</v>
+      </c>
+      <c r="G22" t="n">
+        <v>28</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>610</v>
+      </c>
+      <c r="J22" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -937,12 +1141,12 @@
       <c r="D23" t="n">
         <v>1428</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1163,20 @@
       <c r="D24" t="n">
         <v>2156</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
         <v>295</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>27</v>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1193,12 @@
       <c r="D25" t="n">
         <v>1996</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1215,20 @@
       <c r="D26" t="n">
         <v>3588</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
         <v>177</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>27</v>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1245,12 @@
       <c r="D27" t="n">
         <v>1664</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,11 +1267,27 @@
       <c r="D28" t="n">
         <v>2704</v>
       </c>
-      <c r="E28" t="n">
-        <v>460</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>271</v>
+        <v>432</v>
+      </c>
+      <c r="G28" t="n">
+        <v>27</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>244</v>
+      </c>
+      <c r="J28" t="n">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/11130.xlsx
+++ b/output/roomself_excel/11130.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,46 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -509,6 +549,26 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>160</v>
+      </c>
+      <c r="N2" t="n">
+        <v>27</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -539,6 +599,14 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -561,6 +629,14 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -591,6 +667,26 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>60</v>
+      </c>
+      <c r="N5" t="n">
+        <v>28</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -629,6 +725,38 @@
       <c r="J6" t="n">
         <v>27</v>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>916</v>
+      </c>
+      <c r="N6" t="n">
+        <v>28</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>93</v>
+      </c>
+      <c r="R6" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -659,6 +787,26 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>214</v>
+      </c>
+      <c r="N7" t="n">
+        <v>27</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -697,6 +845,26 @@
       <c r="J8" t="n">
         <v>28</v>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>245</v>
+      </c>
+      <c r="N8" t="n">
+        <v>27</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -727,6 +895,14 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -749,6 +925,14 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -779,6 +963,14 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -801,6 +993,14 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -823,6 +1023,14 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -853,6 +1061,38 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>50</v>
+      </c>
+      <c r="N14" t="n">
+        <v>28</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>108</v>
+      </c>
+      <c r="R14" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -883,6 +1123,14 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -921,6 +1169,26 @@
       <c r="J16" t="n">
         <v>28</v>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>317</v>
+      </c>
+      <c r="N16" t="n">
+        <v>28</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -959,6 +1227,26 @@
       <c r="J17" t="n">
         <v>28</v>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>206</v>
+      </c>
+      <c r="N17" t="n">
+        <v>22</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -997,6 +1285,26 @@
       <c r="J18" t="n">
         <v>27</v>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>138</v>
+      </c>
+      <c r="N18" t="n">
+        <v>28</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1027,6 +1335,26 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>89</v>
+      </c>
+      <c r="N19" t="n">
+        <v>28</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1057,6 +1385,14 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1087,6 +1423,26 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>90</v>
+      </c>
+      <c r="N21" t="n">
+        <v>28</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1123,6 +1479,38 @@
         <v>610</v>
       </c>
       <c r="J22" t="n">
+        <v>28</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>140</v>
+      </c>
+      <c r="N22" t="n">
+        <v>28</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>320</v>
+      </c>
+      <c r="R22" t="n">
         <v>28</v>
       </c>
     </row>
@@ -1147,6 +1535,14 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1177,6 +1573,26 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>115</v>
+      </c>
+      <c r="N24" t="n">
+        <v>27</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1199,6 +1615,14 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1229,6 +1653,26 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>85</v>
+      </c>
+      <c r="N26" t="n">
+        <v>27</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1251,6 +1695,14 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1287,6 +1739,38 @@
         <v>244</v>
       </c>
       <c r="J28" t="n">
+        <v>28</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>89</v>
+      </c>
+      <c r="N28" t="n">
+        <v>27</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>240</v>
+      </c>
+      <c r="R28" t="n">
         <v>28</v>
       </c>
     </row>
